--- a/data/interim/summarizing_management_table.xlsx
+++ b/data/interim/summarizing_management_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">species</t>
   </si>
@@ -35,9 +35,6 @@
     <t xml:space="preserve">Dijle - Dyle</t>
   </si>
   <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
     <t xml:space="preserve">22</t>
   </si>
   <si>
@@ -59,64 +56,73 @@
     <t xml:space="preserve">Zenne - Senne</t>
   </si>
   <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
     <t xml:space="preserve">≤ 21</t>
   </si>
   <si>
     <t xml:space="preserve">Hydrocotyle ranunculoides</t>
   </si>
   <si>
-    <t xml:space="preserve">16</t>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≤ 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≤ 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≤ 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impatiens glandulifera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludwigia grandiflora</t>
   </si>
   <si>
     <t xml:space="preserve">13</t>
   </si>
   <si>
-    <t xml:space="preserve">≤ 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≤ 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≤ 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impatiens glandulifera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludwigia grandiflora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">6</t>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
   </si>
   <si>
     <t xml:space="preserve">Myriophyllum aquaticum</t>
   </si>
   <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
   </si>
 </sst>
 </file>
@@ -473,10 +479,10 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -484,16 +490,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -501,64 +507,64 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>24</v>
@@ -572,13 +578,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
         <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -586,16 +592,16 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -603,7 +609,7 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -612,7 +618,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -623,13 +629,13 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -637,16 +643,16 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -654,13 +660,13 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
@@ -668,50 +674,50 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
         <v>24</v>
